--- a/data/trans_dic/IP1015-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1015-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen parálisis</t>
+          <t>Menores que padecen parálisis (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,14</t>
+          <t>0,0; 4,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,17 +1008,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1027,12 +1028,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1042,7 +1043,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,56</t>
+          <t>0,0; 0,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 3,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,5</t>
+          <t>0,0; 3,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,03</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1337,17 +1338,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,43</t>
+          <t>0,0; 0,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1357,27 +1358,27 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,79</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,59</t>
+          <t>0,0; 0,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,44</t>
+          <t>0,05; 0,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,44</t>
+          <t>0,04; 0,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,35</t>
+          <t>0,0; 0,34</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen parálisis (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4049</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3810</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3762</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3890</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2903</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3531</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3214</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3800</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2119</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3251</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4088</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4462</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2927</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3535</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4122</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4314</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2939</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3455</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2074</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2074</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2521</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2388</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>673; 5586</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 5415</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4822</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>673; 5554</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>607; 6248</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4703</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1015-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1015-Clase-trans_dic.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,15</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,33</t>
+          <t>0,0; 5,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,49</t>
+          <t>0,0; 0,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
     </row>
@@ -1133,32 +1133,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,21</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,19</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,97</t>
+          <t>0,0; 4,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,35</t>
+          <t>0,0; 0,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1353,17 +1353,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,82</t>
+          <t>0,1; 0,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,09; 0,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,68</t>
+          <t>0,0; 0,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1373,12 +1373,12 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,45</t>
+          <t>0,05; 0,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,34</t>
+          <t>0,0; 0,36</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4049</t>
+          <t>0; 3381</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3810</t>
+          <t>0; 3861</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3762</t>
+          <t>0; 4491</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3890</t>
+          <t>0; 3864</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2903</t>
+          <t>0; 3272</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3531</t>
+          <t>0; 3479</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2153,22 +2153,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3214</t>
+          <t>0; 3250</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3800</t>
+          <t>0; 4215</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2119</t>
+          <t>0; 2632</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3251</t>
+          <t>0; 2919</t>
         </is>
       </c>
     </row>
@@ -2306,32 +2306,32 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4088</t>
+          <t>0; 3507</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4462</t>
+          <t>0; 3487</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2927</t>
+          <t>0; 3226</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3535</t>
+          <t>0; 3513</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4122</t>
+          <t>0; 3453</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4314</t>
+          <t>0; 3590</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 2939</t>
+          <t>0; 3055</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3455</t>
+          <t>0; 3073</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2388</t>
+          <t>0; 2611</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2632,32 +2632,32 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>673; 5586</t>
+          <t>673; 5529</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 5415</t>
+          <t>611; 5980</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 4822</t>
+          <t>0; 4236</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>673; 5554</t>
+          <t>672; 5622</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>607; 6248</t>
+          <t>747; 6211</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4703</t>
+          <t>0; 5021</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1015-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1015-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,7 +625,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,23%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,61</t>
+          <t>0,0; 0,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>0,07%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,1; 0,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,39</t>
+          <t>0,08; 0,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 0,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,84</t>
+          <t>0,0; 0,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,42</t>
+          <t>0,05; 0,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,45</t>
+          <t>0,05; 0,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,36</t>
+          <t>0,0; 0,35</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>673</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4039</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3381</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3861</t>
+          <t>0; 4016</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3067</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4491</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3864</t>
+          <t>0; 3752</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>700</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>480</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3537</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3272</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3551</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3479</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2542</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3250</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4215</t>
+          <t>0; 3790</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2632</t>
+          <t>0; 2412</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 2919</t>
+          <t>0; 3260</t>
         </is>
       </c>
     </row>
@@ -2185,32 +2185,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>700</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>687</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>718</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3142</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3441</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3631</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3507</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3487</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3226</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3513</t>
+          <t>0; 3227</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3453</t>
+          <t>0; 3481</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 3590</t>
+          <t>0; 4820</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>607</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3329</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3055</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3073</t>
+          <t>0; 2529</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>480</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2074</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2041</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>669; 5599</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2611</t>
+          <t>605; 5637</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4165</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>673; 5529</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>611; 5980</t>
+          <t>0; 2897</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 4236</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>672; 5622</t>
+          <t>672; 5769</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>747; 6211</t>
+          <t>689; 6126</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 5021</t>
+          <t>0; 4786</t>
         </is>
       </c>
     </row>
